--- a/data/processed/harmonization/Nitrogen__Total_nitrogen/10.15485_1835182/10.15485_1835182_soil_Nitrogen__Total_nitrogen.xlsx
+++ b/data/processed/harmonization/Nitrogen__Total_nitrogen/10.15485_1835182/10.15485_1835182_soil_Nitrogen__Total_nitrogen.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
@@ -523,7 +523,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -567,7 +567,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -611,7 +611,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -655,7 +655,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -699,7 +699,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -787,7 +787,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -831,7 +831,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -914,12 +914,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>LDW:10</t>
+          <t>LDW:1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -958,12 +958,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>LDW:11</t>
+          <t>LDW:2</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>LDW:12</t>
+          <t>LDW:3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>LDW:13</t>
+          <t>LDW:4</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>LDW:14</t>
+          <t>LDW:5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>LDW:15</t>
+          <t>LDW:6</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>LDW:16</t>
+          <t>LDW:7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>LDW:17</t>
+          <t>LDW:8</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>LDW:18</t>
+          <t>LDW:9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SCBI:19</t>
+          <t>SCBI:114</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SCBI:20</t>
+          <t>SCBI:169</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>SCBI:21</t>
+          <t>SCBI:1219</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>SCBI:22</t>
+          <t>SCBI:1228</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>SCBI:23</t>
+          <t>SCBI:1425</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SCBI:24</t>
+          <t>SCBI:1530</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>SCBI:25</t>
+          <t>SCBI:1532</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>SCBI:26</t>
+          <t>SCBI:1906</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>SCBI:27</t>
+          <t>SCBI:1928</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>SRC:28</t>
+          <t>SRC:367</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>SRC:29</t>
+          <t>SRC:412</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>SRC:30</t>
+          <t>SRC:450</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SRC:31</t>
+          <t>SRC:613</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1882,12 +1882,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>SRC:32</t>
+          <t>SRC:832</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1926,12 +1926,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>SRC:33</t>
+          <t>SRC:1050</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>SRC:34</t>
+          <t>SRC:1105</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -2014,12 +2014,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>SRC:35</t>
+          <t>SRC:1219</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>SRC:36</t>
+          <t>SRC:1347</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>TRC:37</t>
+          <t>TRC:1</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -2146,12 +2146,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>TRC:38</t>
+          <t>TRC:2</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>TRC:39</t>
+          <t>TRC:3</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>TRC:40</t>
+          <t>TRC:4</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -2278,12 +2278,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>TRC:41</t>
+          <t>TRC:5</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>TRC:42</t>
+          <t>TRC:6</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>TRC:43</t>
+          <t>TRC:7</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>TRC:44</t>
+          <t>TRC:8</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2454,12 +2454,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>TRC:45</t>
+          <t>TRC:9</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2498,12 +2498,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>WLF:46</t>
+          <t>WLF:1</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>WLF:47</t>
+          <t>WLF:2</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>WLF:48</t>
+          <t>WLF:3</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>WLF:49</t>
+          <t>WLF:4</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>WLF:50</t>
+          <t>WLF:5</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>WLF:51</t>
+          <t>WLF:6</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>WLF:52</t>
+          <t>WLF:7</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -2806,12 +2806,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>WLF:53</t>
+          <t>WLF:8</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -2850,12 +2850,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>WLF:54</t>
+          <t>WLF:9</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Site:ID</t>
+          <t>Site:Plot</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
